--- a/education_forms/029_founding_documents_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/029_founding_documents_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Where was the U.S. Declaration of Independence adopted</t>
+          <t>Declaration Of Independence Location2 Page</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Who signed the U.S. Declaration of Independence</t>
+          <t>U S Declaration Of Independence Signatory Page</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>founding_documents_page</t>
+          <t>founding_documents_page_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>u_s_declaration_of_independence_page</t>
+          <t>u_s_declaration_of_independence_page_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the U.S. Declaration of Independence</t>
+          <t>U S Declaration Of Independence Page 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>u_s_declaration_of_independence_page</t>
+          <t>u_s_declaration_of_independence_page_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the U.S. Declaration of Independence</t>
+          <t>U S Declaration Of Independence Page 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>founding_documents_page_choices</t>
+          <t>founding_documents_page_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>founding_documents_page_choices</t>
+          <t>founding_documents_page_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>u_s_declaration_of_independence_page_choices</t>
+          <t>u_s_declaration_of_independence_page_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>u_s_declaration_of_independence_page_choices</t>
+          <t>u_s_declaration_of_independence_page_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
